--- a/memory/Test_Checkliste_1n_iPad.xlsx
+++ b/memory/Test_Checkliste_1n_iPad.xlsx
@@ -431,7 +431,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -470,7 +470,11 @@
           <t>Login mit admin/admin123 funktioniert</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -486,7 +490,11 @@
           <t>Session-Timer wird angezeigt (oben rechts)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>OK - Session: 29:59</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -518,7 +526,11 @@
           <t>Import einer Excel-Datei mit je einem Schüler pro Zeile</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -534,7 +546,11 @@
           <t>Neue Schüler werden korrekt angelegt</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -550,7 +566,11 @@
           <t>Neue iPads werden korrekt angelegt</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -566,7 +586,11 @@
           <t>Zuordnungen werden korrekt erstellt</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -582,7 +606,11 @@
           <t>Import-Zusammenfassung zeigt korrekte Zahlen</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -598,7 +626,11 @@
           <t>Schüler auf 2 Zeilen (2 iPads) → erhält beide iPads</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -614,7 +646,11 @@
           <t>Schüler auf 3 Zeilen → erhält alle 3 iPads</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -630,7 +666,11 @@
           <t>Schüler wird nur einmal in DB angelegt (nicht dupliziert)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -662,7 +702,11 @@
           <t>Schüler auf 4+ Zeilen → nur 3 iPads zugewiesen</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -678,7 +722,11 @@
           <t>Fehlermeldung für übersprungene Zuordnungen</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -886,7 +934,11 @@
           <t>Export erstellt gültige .xlsx Datei</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -902,7 +954,11 @@
           <t>Jede Zuordnung ist eine separate Zeile</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -918,7 +974,11 @@
           <t>Schüler mit 2 iPads → erscheint auf 2 Zeilen</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -934,7 +994,11 @@
           <t>Schüler mit 3 iPads → erscheint auf 3 Zeilen</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1030,7 +1094,11 @@
           <t>Exportierte Datei kann reimportiert werden</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1078,7 +1146,11 @@
           <t>iPad zuordnen Button bei Schüler mit &lt;3 iPads sichtbar</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1094,7 +1166,11 @@
           <t>Klick öffnet Auswahl-Dialog für verfügbare iPads</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1158,7 +1234,11 @@
           <t>Schüler mit 3 iPads zeigt 'Limit erreicht'</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>OK - Peter Müller zeigt 'Limit erreicht'</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1174,7 +1254,11 @@
           <t>'Limit erreicht' Button ist deaktiviert/ausgegraut</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1190,7 +1274,11 @@
           <t>Badge zeigt '3 iPad(s)' an</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1286,7 +1374,11 @@
           <t>Tabelle zeigt alle Schüler</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OK - 4 Schüler angezeigt</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1302,7 +1394,11 @@
           <t>'iPad-Status' Spalte zeigt Anzahl der iPads</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1318,7 +1414,11 @@
           <t>Sortierung nach Name funktioniert</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1350,7 +1450,11 @@
           <t>Filter nach Vorname funktioniert</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1366,7 +1470,11 @@
           <t>Filter nach Nachname funktioniert</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1382,7 +1490,11 @@
           <t>Filter nach Klasse funktioniert</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1398,7 +1510,11 @@
           <t>'Neuen Schüler anlegen' Button funktioniert</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1478,7 +1594,11 @@
           <t>Einzelner Schüler kann gelöscht werden</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OK - BUG BEHOBEN: Jetzt alle iPads freigegeben</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -1510,7 +1630,11 @@
           <t>Alle Zuordnungen werden aufgelöst</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OK - BUG BEHOBEN: 1:n korrekt behandelt</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -1526,7 +1650,11 @@
           <t>Zugehörige iPads werden freigegeben</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OK - BUG BEHOBEN: Alle iPads freigegeben</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -1590,7 +1718,11 @@
           <t>Tabelle zeigt alle iPads</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OK - 9 iPads angezeigt</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -1606,7 +1738,11 @@
           <t>Status-Spalte zeigt 'verfügbar' oder 'zugewiesen'</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -1670,7 +1806,11 @@
           <t>'Neues iPad anlegen' Button funktioniert</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -1798,7 +1938,11 @@
           <t>Alle aktiven Zuordnungen werden angezeigt</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OK - 7 Zuordnungen</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -1910,7 +2054,11 @@
           <t>'Alle Zuordnungen exportieren' Button funktioniert</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -1942,7 +2090,11 @@
           <t>iPad-Typ (Standard) kann geändert werden</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -1990,7 +2142,11 @@
           <t>'Bestandsliste exportieren' Button funktioniert</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>OK - UI verifiziert</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -2086,7 +2242,11 @@
           <t>Schüler mit exakt 3 iPads → Limit erreicht</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>OK - Peter Müller</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -2102,7 +2262,11 @@
           <t>Versuch 4. iPad zuzuweisen → wird korrekt abgelehnt</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>OK - Automatisiert getestet</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
